--- a/table/resources/sample/BundleGiftPack.xlsx
+++ b/table/resources/sample/BundleGiftPack.xlsx
@@ -39,6 +39,28 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+第一个参数必须是 【金币】</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
@@ -92,13 +114,13 @@
     <t>ChannelCommodity</t>
   </si>
   <si>
-    <t>1990000_10000|1980000_1000</t>
+    <t>1990000_1000000|1980000_1000|1024001_20000|1024007_20</t>
   </si>
   <si>
-    <t>1990000_10000|1980000_1001</t>
+    <t>1990000_2000000|1980000_1001</t>
   </si>
   <si>
-    <t>1960000_10000|1022502_100</t>
+    <t>1990000_5000000|1022502_100|1960000_100000</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1094,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="34.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="74.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="30.625" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
